--- a/data/ted_procurements.xlsx
+++ b/data/ted_procurements.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2333,6 +2333,38 @@
           <t>SEK</t>
         </is>
       </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>142</v>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Pohjois-Pohjanmaan hyvinvointialue, Kainuun hyvinvointialue, Lapin hyvinvointialue, Keski-Pohjanmaan hyvinvointialue</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>medac Gesellschaft für klinische Spezialpräparate G.m.b.H, sivuliike Suomessa, Ailon Pharma Oy, Abacus Medicine A/S, ALK-Abéllo Nordic A/S, AOP Orphan Pharmaceuticals Sweden AB, AbbVie Oy, Abboxia AB, Abcur AB, Abena Finland OY, Accord Healthcare Oy, Aguettant Nordic ApS, Alexion Pharma Nordics AB, Aspen Pharma Ireland Limited, Astellas Pharma a/s, AstraZeneca Oy, Avansor Pharma Oy, Avia Pharma Oy, B. Braun Medical Oy, Bausch &amp; Lomb Nordic AB, Baxter Oy, Bayer Oy, Amgen Aktiebolag, filial i Finland, Berlin-Chemie/A. Menarini Suomi Oy, Berner Oy, betapharm Arzneimittel GmbH, 2care4 Aps, filial, BioGaia Finland Oy, Biocodex Oy, Bioglan AB, Boehringer Ingelheim Finland Ky, Bracco Imaging Scandinavia AB, Biogen Finland Oy, CNX Therapeutics Ltd, CSL Behring AB, CampusPharma AB, Camurus AB, Celltrion Healthcare Finland Oy, Chiesi Pharma AB, Danone Oy, Desitin Pharma Oy, EQL Pharma AB, Eisai AB, Essential Pharma Limited, Evolan Pharma AB, Exeltis Sverige AB, filial i Finland, Fresenius Medical Care Suomi Oy, Ferring Lääkkeet Oy, Fresenius Kabi Ab, Sivuliike Suomessa, FrostPharma AB, Fysioline Oy, G.L. Pharma Nordic AB, GHN Pharma Nordic AB, Galderma Nordic AB, Galenica AB, Gedeon Richter Nordics AB, Gilead Sciences Finland Oy, GlaxoSmithKline Oy, Glenmark Pharmaceuticals Nordic AB, Grifols Nordic AB, Grindeks Kalceks Suomi Oy, Grünenthal Finland Oy, Haleon Finland Oy, hameln pharma gmbh, Horus Pharma Nordic, IBSA Nordic, Immedica Pharma Ab, Gentili Pharma AS, Institut Produits Synthése (IPSEN) AB, Janssen-Cilag Oy, Jazz Pharmceuticals Denmark ApS, KRKA Finland Oy, Karo Healthcare AB, KEBOMED Oy, KiiltoClean Oy, Kir-Fix Oy, Kurantis Aps, Kyowa Kirin AB, LEO Pharma Oy, MIP Pharma GmbH, MSD Finland Oy, Macure Pharma ApS, Magnum Medical Finland Oy, Medans Oy, Medical Valley Invest AB, Mediq Suomi Oy, Medtronic Finland Oy, Merck Oy, Mundipharma Oy, Navamedic AB, neuraxpharm Sweden AB, Nordic Drugs AB, sivuliike Suomessa, Nordic Prime ApS, NordicInfu Care AB - Filial Finland, Norgine Danmark A/S, Novartis Finland Oy, Novo Nordisk Farma Oy, Octapharma Nordic AB, sivuliike Suomessa, OneMed Oy, Öresund Pharma Aps, Organon Finland Oy, Orifarm Healthcare Oy, Orifarm Oy, Orion Oyj, Otsuka Pharma Scandinavia AB, Oy Bristol-Myers Squibb (Finland) Ab, Oy Eli Lilly Finland Ab, Oy GE Healthcare Bio-Sciences Ab, Oy H. Lundbeck Ab, Oy Swedish Orphan Biovitrum Ab, Oy Verman Ab, POA Pharma Scandinavia Ab, filial Finland, Panpharma Nordic AS, Paranova OY, Perrigo Suomi Oy, Pfizer Oy, Pharmanovia A/S, Pierrel S.p.A., Prothya Biololutions Finland Oy, Recordati AB, Roche Oy, SAM Nordic Oy, Serb SA, STADA Nordic ApS, Suomen sivuliike, Sabora Pharma Oy, Sandoz A/S, Sanofi Oy, Scandinavian Biopharma Distribution, SERVIER FINLAND OY, Stella Nordic Oy, Stragen Finland Oy, Sun Pharmaceuticals GmbH, Suomen Nestlé Oy, TD Pharma B.V., Takeda Oy, Teva Finland Oy, Tillotts Pharma Ab, UAB Norameda, UCB Pharma Oy Finland, Unimedic Pharma AB, Vantive Oy, Viatris Oy, Vifor Pharma Nordiska AB</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3063,7 +3095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y66"/>
+  <dimension ref="A1:Y67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9292,12 +9324,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>LOT-0001</t>
+          <t>LOT-0002</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Kravspec Läkemedel</t>
+          <t>Administrativa föreskrifter</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -9308,7 +9340,7 @@
       <c r="F65" s="3" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="3" t="n">
-        <v>244000000</v>
+        <v>488000000</v>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
@@ -9344,11 +9376,11 @@
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2027-02-28</t>
         </is>
       </c>
       <c r="R65" s="2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="S65" s="2" t="n">
         <v>42</v>
@@ -9391,12 +9423,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>LOT-0002</t>
+          <t>LOT-0001</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Administrativa föreskrifter</t>
+          <t>Kravspec Läkemedel</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -9407,7 +9439,7 @@
       <c r="F66" s="3" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="3" t="n">
-        <v>488000000</v>
+        <v>244000000</v>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
@@ -9443,11 +9475,11 @@
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="R66" s="2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="S66" s="2" t="n">
         <v>42</v>
@@ -9475,6 +9507,93 @@
       </c>
       <c r="Y66" s="2" t="n">
         <v>42</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Pohjois-Pohjanmaan hyvinvointialue, Kainuun hyvinvointialue, Lapin hyvinvointialue, Keski-Pohjanmaan hyvinvointialue</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>LOT-0000</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Lääkevalmisteet ja niihin rinnastettavat tuotteet hankintakaudelle 1.1.2026-31.12.2027</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="3" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="3" t="n">
+        <v>142</v>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>Finland – Pharmaceutical products – Lääkevalmisteet ja niihin rinnastettavat tuotteet hankintakaudelle 1.1.2026-31.12.2027</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>618924-2026</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="n">
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/data/ted_procurements.xlsx
+++ b/data/ted_procurements.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2087,100 +2087,106 @@
       <c r="H49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>Historical</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="n">
+        <v>244000000</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+        </is>
+      </c>
+      <c r="E50" s="1" t="n">
+        <v>840000000</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Øresund Pharma ApS, Vingmed AB, Viatris AB, Unimedic Pharma AB, Recordati AB, Orifarm Generics AB, Orifarm AB, Nordic Drugs Aktiebolag, Navamedic AB, Mölnlycke Health Care AB, Macure Pharma, Krka Sverige AB, Karo Healthcare AB, Janssen-Cilag Aktiebolag, hameln pharma AB, Haleon Sweden AB, Glenmark Pharmaceuticals Nordic AB, GE Healthcare Aktiebolag, G.L. Pharma Nordic Aktiebolag, FrostPharma AB, Exeltis Sverige AB, Ebb Medical, Camurus AB, Bioglan AB, BD Infection Prevention BV, Baxter Medical AB, B.Braun Medical AB, Aspen Pharma Ireland Limited, Aguettant Nordic ApS, Abboxia AB, Bayer Aktiebolag, Øresund Pharma ApS, Vingmed AB, Viatris AB, Unimedic Pharma AB, Recordati AB, Orifarm Generics AB, Orifarm AB, Nordic Drugs Aktiebolag, Navamedic AB, Mölnlycke Health Care AB, Macure Pharma, Krka Sverige AB, Karo Healthcare AB, Janssen-Cilag Aktiebolag, hameln pharma AB, Haleon Sweden AB, Glenmark Pharmaceuticals Nordic AB, GE Healthcare Aktiebolag, G.L. Pharma Nordic Aktiebolag, FrostPharma AB, Exeltis Sverige AB, Ebb Medical, Camurus AB, Bioglan AB, BD Infection Prevention BV, Baxter Medical AB, B.Braun Medical AB, Aspen Pharma Ireland Limited, Aguettant Nordic ApS, Abboxia AB, Bayer Aktiebolag</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>2024-02-15Z</t>
         </is>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="C51" s="3" t="n">
         <v>410000000</v>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Region Västernorrland</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Abboxia AB, Abcur AB, Accord Healthcare AB, Bayer Aktiebolag, CAMPUS Pharma AB, Camurus AB, CSL Behring Aktiebolag, EQL Pharma AB, Gilead Sciences Sweden AB, Fresenius Kabi AB, Fresenius Medical Care Sverige AB, FrostPharma AB, Institut Produits Synthése (IPSEN) AB, Macure Pharma, medac, Mylan AB, Octapharma Nordic AB, Tillotts Pharma AB, Swedish Orphan Biovitrum AB (publ), Roche Aktiebolag, UCB Pharma AB, Teva Sweden Aktiebolag, Takeda Pharma AB, Stragen Nordic A/S, STADA Nordic ApS, Scandinavian Biopharma Distribution AB, AOP Orphan Pharmaceuticals GmbH, Baxter Medical AB, MIP Pharma GmbH, Sandoz A/S, Pfizer Aktiebolag, Sanofi AB, Novartis Sverige Aktiebolag, AbbVie AB, Merz Therapeutics Nordics AB, Abboxia AB, Abcur AB, Accord Healthcare AB, Bayer Aktiebolag, CAMPUS Pharma AB, Camurus AB, EQL Pharma AB, Gilead Sciences Sweden AB, Fresenius Medical Care Sverige AB, FrostPharma AB, Institut Produits Synthése (IPSEN) AB, Macure Pharma, medac, Octapharma Nordic AB, Tillotts Pharma AB, Roche Aktiebolag, Teva Sweden Aktiebolag, Takeda Pharma AB, Scandinavian Biopharma Distribution AB, AOP Orphan Pharmaceuticals GmbH, MIP Pharma GmbH, Novartis Sverige Aktiebolag, AbbVie AB, Merz Therapeutics Nordics AB, Abboxia AB, Abcur AB, Accord Healthcare AB, Bayer Aktiebolag, CAMPUS Pharma AB, Camurus AB, CSL Behring Aktiebolag, EQL Pharma AB, Gilead Sciences Sweden AB, Fresenius Kabi AB, Fresenius Medical Care Sverige AB, FrostPharma AB, Institut Produits Synthése (IPSEN) AB, Macure Pharma, medac, Mylan AB, Octapharma Nordic AB, Tillotts Pharma AB, Swedish Orphan Biovitrum AB (publ), Roche Aktiebolag, UCB Pharma AB, Teva Sweden Aktiebolag, Takeda Pharma AB, Stragen Nordic A/S, STADA Nordic ApS, Scandinavian Biopharma Distribution AB, AOP Orphan Pharmaceuticals GmbH, Baxter Medical AB, MIP Pharma GmbH, Sandoz A/S, Pfizer Aktiebolag, Sanofi AB, Novartis Sverige Aktiebolag, AbbVie AB, Merz Therapeutics Nordics AB</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>Historical</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>2024-03-11Z</t>
         </is>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C52" s="1" t="n">
         <v>70000000</v>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Region Jönköpings Län</t>
         </is>
       </c>
-      <c r="E51" s="1" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
+      <c r="E52" s="1" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
         <is>
           <t>Orifarm AB, Mylan AB, CAMPUS Pharma AB, hameln pharma AB, Abcur AB, Unimedic Pharma AB, Teva Sweden Aktiebolag, Baxter Medical AB, Orifarm Generics AB, Macure Pharma, Bioglan AB, Accord Healthcare AB, STADA Nordic ApS, Otsuka Pharma Scandinavia AB, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Bristol-Myers Squibb Aktiebolag, UCB Pharma AB, Sun Pharmaceutical Germany GmbH, Swedish Orphan Biovitrum AB (publ), Bayer Aktiebolag, PANPHARMA NORDIC AS, MIP Pharma GmbH, Oresund Pharma ApS, Orifarm AB, Mylan AB, CAMPUS Pharma AB, hameln pharma AB, Abcur AB, Unimedic Pharma AB, Teva Sweden Aktiebolag, Baxter Medical AB, Orifarm Generics AB, Macure Pharma, Bioglan AB, Accord Healthcare AB, STADA Nordic ApS, Otsuka Pharma Scandinavia AB, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Bristol-Myers Squibb Aktiebolag, UCB Pharma AB, Sun Pharmaceutical Germany GmbH, Swedish Orphan Biovitrum AB (publ), Bayer Aktiebolag, PANPHARMA NORDIC AS, MIP Pharma GmbH, Oresund Pharma ApS</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>2024-04-12Z</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="n">
-        <v>130000000</v>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Sansia Oy, Pohjois-Savon hyvinvointialue, Etelä-Savon hyvinvointialue, Pohjois-Karjalan hyvinvointialue, Keski-Suomen hyvinvointialue</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>Abacus Medicine, AbbVie Oy, Alexion Pharma Nordics Ab, Amgen Ab, AstraZeneca, Daiichi Sankyo Nordics ApS, Fresenius Kabi Ab, Gilead Sciences Finland Oy, GlaxoSmithKline Oy, Incyte Biosciences Finland Oy, Janssen-Cilag OY, Novartis Finland Oy, Oy Swedish Orphan Biovitrum Ab, Pfizer Oy, Sanofi Oy, Takeda Oy, Vifor Pharma Nordiska AB, Prothya Biosolutions Finland Oy, Prothya Biosolutions Finland Oy, 2care4 ApS, filial, 2care4 Generics ApS, Abboxia AB, Abcur AB, Abena Finland OY, Accord Healthcare Oy, Aguettant Nordic ApS, Ailon Pharma Oy, ALK-ABELLO Nordic AS, AOP Orphan Pharmaceuticals Sweden AB, Aspen Pharma Ireland Limited, Astellas Pharma AS Suomen sivuliike, Avansor Pharma Oy, B. Braun Medical Oy, Bausch Lomb Nordic, Baxter Oy, Bayer Oy, Becton Dickinson Finland Oy, Berner Oy, Betapharm Arzneimittel GmbH, Biocodex Oy, BioGaia Finland Oy, Bioglan AB, Boehringer Ingelheim Finland Ky, Bracco Imaging Scandinavia, Campus Pharma, Camurus AB, Cheplapharm Arzneimittel GmbH, Chiesi Pharma Ab, CNX Therapeutics Ltd., CORZA MEDICAL DISTRIBUTION GMBH, CSL Behring AB, Danone Oy, Decem Pharma Oy, Desitin Pharma Oy, DNE PHARMA AS, EISAI AB, EQL Pharma AB, Evolan Pharma Oy, Exeltis Sverige AB, filial i Finland, Ferring Lääkkeet Oy, Finnomedical Oy, Fresenius Medical Care Suomi Oy, Frost Pharma AB, Galderma Nordic AB, GALENICA AB, Gedeon Richter Nordics Ab, Glenmark Pharmaceuticals Nordic AB, Grex Medical Oy, Grünenthal Finland Oy, Haleon Finland Oy, IBSA Nordic, Indivior Europe Limited, Iogen Oy, Janssen-Cilag Oy, Johnson Johnson Finland, Karo Pharma AB, Kebomed Oy, KRKA Finland Oy, Kurantis ApS, Kyowa Kirin AB, LEO Pharma Oy, Macure Pharma Aps, Magnum Medical Finland Oy, Medac Gesellschaft für klinische Spezialpräparate G.m.b.H, sivuliike Suomessa, Medans Oy, Mediplast Fenno Oy, Mediq Suomi Oy, MIP Pharma GmbH, MSD Finland Oy, Mundipharma Oy, Navamedic AB filial i Finland, Neuraxpharm Sweden AB, Nordic Drugs AB, Nordic Prime ApS, Nordicinfu Care AB - Filial Finland, Norgine Danmark AS, Novo Nordisk Farma Oy, Octapharma Nordic AB, sivuliike Suomessa, OneMed Oy, Oresund Pharma ApS, Organon Finland Oy, Orifarm Healthcare Oy, Orifarm Oy, Orion Oy, Orphalan Limited, Otsuka Pharma Scandinavia AB, Oy Bristol-Myers Squibb Finland Ab, Oy Eli Lilly Finland Ab, Oy GE Healthcare Bio-Sciences Ab, Oy H. Lundbeck Ab, Oy Verman Ab, Panpharma Nordic AS, Paranova Oy, Perrigo Suomi Oy, Pharmacosmos AS, Pharmanovia A/S, POA Pharma Scandinavia AB, filial i Finland, Recordati AB, Roche Oy, Sabora Pharma Oy, SAM Nordic Oy, Sandoz AS, Serb SA, Servier Finland Oy, Shionogi B.V., STADA Nordic ApS, Stella Nordic Oy, Stragen Finland Oy, Sun Pharmaceutical Germany GmbH, Suomen Nestlé, Teva Finland Oy, Tillotts Pharma Ab, UAB Norameda, UCB Pharma Oy Finland, Unimedic Pharma AB, Viatris Oy, Winmed Nordic ApS, VITAL PHARMA NORDIC ApS</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2190,35 +2196,29 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>2024-04-24Z</t>
+          <t>2024-04-12Z</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
-        <v>500000000</v>
+        <v>130000000</v>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Region Stockholm - Serviceförvaltningen</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>1000000000</v>
-      </c>
+          <t>Sansia Oy, Pohjois-Savon hyvinvointialue, Etelä-Savon hyvinvointialue, Pohjois-Karjalan hyvinvointialue, Keski-Suomen hyvinvointialue</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Abcur AB, Accord Healthcare AB, B.Braun Medical AB, Bayer Aktiebolag, Bioglan AB, Boehringer Ingelheim AB, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, hameln pharma AB, Janssen-Cilag Aktiebolag, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Norgine A/S, Otsuka Pharma Scandinavia AB, PANPHARMA NORDIC AS, Orifarm AB, Roche Aktiebolag, Sandoz A/S, STADA Nordic ApS, Sanofi AB, Sun Pharmaceutical Germany GmbH, Takeda Pharma AB, Teva Sweden Aktiebolag, Viatris AB, Abboxia AB, Abcur AB, Accord Healthcare AB, Aspen Pharma Ireland Limited, B.Braun Medical AB, Bayer Aktiebolag, Bioglan AB, Boehringer Ingelheim AB, CSL Behring Aktiebolag, Ebb Medical, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, Galderma Nordic AB, Gilead Sciences Sweden AB, Glenmark Pharmaceuticals Nordic AB, hameln pharma AB, Indivior Europe Limited, Janssen-Cilag Aktiebolag, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Norgine A/S, Orifarm Generics AB, Otsuka Pharma Scandinavia AB, PANPHARMA NORDIC AS, Pfizer Aktiebolag, Orifarm AB, Oresund Pharma ApS, Roche Aktiebolag, Sandoz A/S, STADA Nordic ApS, Sanofi AB, Sun Pharmaceutical Germany GmbH, Takeda Pharma AB, Teva Sweden Aktiebolag, Swedish Orphan Biovitrum AB (publ), Viatris AB</t>
+          <t>Abacus Medicine, AbbVie Oy, Alexion Pharma Nordics Ab, Amgen Ab, AstraZeneca, Daiichi Sankyo Nordics ApS, Fresenius Kabi Ab, Gilead Sciences Finland Oy, GlaxoSmithKline Oy, Incyte Biosciences Finland Oy, Janssen-Cilag OY, Novartis Finland Oy, Oy Swedish Orphan Biovitrum Ab, Pfizer Oy, Sanofi Oy, Takeda Oy, Vifor Pharma Nordiska AB, Prothya Biosolutions Finland Oy, Prothya Biosolutions Finland Oy, 2care4 ApS, filial, 2care4 Generics ApS, Abboxia AB, Abcur AB, Abena Finland OY, Accord Healthcare Oy, Aguettant Nordic ApS, Ailon Pharma Oy, ALK-ABELLO Nordic AS, AOP Orphan Pharmaceuticals Sweden AB, Aspen Pharma Ireland Limited, Astellas Pharma AS Suomen sivuliike, Avansor Pharma Oy, B. Braun Medical Oy, Bausch Lomb Nordic, Baxter Oy, Bayer Oy, Becton Dickinson Finland Oy, Berner Oy, Betapharm Arzneimittel GmbH, Biocodex Oy, BioGaia Finland Oy, Bioglan AB, Boehringer Ingelheim Finland Ky, Bracco Imaging Scandinavia, Campus Pharma, Camurus AB, Cheplapharm Arzneimittel GmbH, Chiesi Pharma Ab, CNX Therapeutics Ltd., CORZA MEDICAL DISTRIBUTION GMBH, CSL Behring AB, Danone Oy, Decem Pharma Oy, Desitin Pharma Oy, DNE PHARMA AS, EISAI AB, EQL Pharma AB, Evolan Pharma Oy, Exeltis Sverige AB, filial i Finland, Ferring Lääkkeet Oy, Finnomedical Oy, Fresenius Medical Care Suomi Oy, Frost Pharma AB, Galderma Nordic AB, GALENICA AB, Gedeon Richter Nordics Ab, Glenmark Pharmaceuticals Nordic AB, Grex Medical Oy, Grünenthal Finland Oy, Haleon Finland Oy, IBSA Nordic, Indivior Europe Limited, Iogen Oy, Janssen-Cilag Oy, Johnson Johnson Finland, Karo Pharma AB, Kebomed Oy, KRKA Finland Oy, Kurantis ApS, Kyowa Kirin AB, LEO Pharma Oy, Macure Pharma Aps, Magnum Medical Finland Oy, Medac Gesellschaft für klinische Spezialpräparate G.m.b.H, sivuliike Suomessa, Medans Oy, Mediplast Fenno Oy, Mediq Suomi Oy, MIP Pharma GmbH, MSD Finland Oy, Mundipharma Oy, Navamedic AB filial i Finland, Neuraxpharm Sweden AB, Nordic Drugs AB, Nordic Prime ApS, Nordicinfu Care AB - Filial Finland, Norgine Danmark AS, Novo Nordisk Farma Oy, Octapharma Nordic AB, sivuliike Suomessa, OneMed Oy, Oresund Pharma ApS, Organon Finland Oy, Orifarm Healthcare Oy, Orifarm Oy, Orion Oy, Orphalan Limited, Otsuka Pharma Scandinavia AB, Oy Bristol-Myers Squibb Finland Ab, Oy Eli Lilly Finland Ab, Oy GE Healthcare Bio-Sciences Ab, Oy H. Lundbeck Ab, Oy Verman Ab, Panpharma Nordic AS, Paranova Oy, Perrigo Suomi Oy, Pharmacosmos AS, Pharmanovia A/S, POA Pharma Scandinavia AB, filial i Finland, Recordati AB, Roche Oy, Sabora Pharma Oy, SAM Nordic Oy, Sandoz AS, Serb SA, Servier Finland Oy, Shionogi B.V., STADA Nordic ApS, Stella Nordic Oy, Stragen Finland Oy, Sun Pharmaceutical Germany GmbH, Suomen Nestlé, Teva Finland Oy, Tillotts Pharma Ab, UAB Norameda, UCB Pharma Oy Finland, Unimedic Pharma AB, Viatris Oy, Winmed Nordic ApS, VITAL PHARMA NORDIC ApS</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2228,109 +2228,109 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
+          <t>2024-04-24Z</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Region Stockholm - Serviceförvaltningen</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Abcur AB, Accord Healthcare AB, B.Braun Medical AB, Bayer Aktiebolag, Bioglan AB, Boehringer Ingelheim AB, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, hameln pharma AB, Janssen-Cilag Aktiebolag, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Norgine A/S, Otsuka Pharma Scandinavia AB, PANPHARMA NORDIC AS, Orifarm AB, Roche Aktiebolag, Sandoz A/S, STADA Nordic ApS, Sanofi AB, Sun Pharmaceutical Germany GmbH, Takeda Pharma AB, Teva Sweden Aktiebolag, Viatris AB, Abboxia AB, Abcur AB, Accord Healthcare AB, Aspen Pharma Ireland Limited, B.Braun Medical AB, Bayer Aktiebolag, Bioglan AB, Boehringer Ingelheim AB, CSL Behring Aktiebolag, Ebb Medical, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, Galderma Nordic AB, Gilead Sciences Sweden AB, Glenmark Pharmaceuticals Nordic AB, hameln pharma AB, Indivior Europe Limited, Janssen-Cilag Aktiebolag, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, Norgine A/S, Orifarm Generics AB, Otsuka Pharma Scandinavia AB, PANPHARMA NORDIC AS, Pfizer Aktiebolag, Orifarm AB, Oresund Pharma ApS, Roche Aktiebolag, Sandoz A/S, STADA Nordic ApS, Sanofi AB, Sun Pharmaceutical Germany GmbH, Takeda Pharma AB, Teva Sweden Aktiebolag, Swedish Orphan Biovitrum AB (publ), Viatris AB</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>2024-05-15Z</t>
         </is>
       </c>
-      <c r="C54" s="3" t="n">
+      <c r="C55" s="3" t="n">
         <v>268138000</v>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
         </is>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="E55" s="3" t="n">
         <v>447642000</v>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Abcur AB, Aspen Pharma Ireland Limited, AstraZeneca AB, B.Braun Medical AB, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, Gilead Sciences Sweden AB, Krka Sverige AB, Macure Pharma, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, MIP Pharma GmbH, Mylan AB, Navamedic AB, Oresund Pharma ApS, PANPHARMA NORDIC AS, Pfizer Aktiebolag, Sandoz A/S, STADA Nordic ApS, Stragen Nordic A/S, Sun Pharmaceutical Germany GmbH, Tillotts Pharma AB, Unimedic Pharma AB, Abcur AB, Aspen Pharma Ireland Limited, AstraZeneca AB, B.Braun Medical AB, EQL Pharma AB, Fresenius Kabi AB, FrostPharma AB, Gilead Sciences Sweden AB, Krka Sverige AB, Macure Pharma, Merck Sharp &amp; Dohme (Sweden) Aktiebolag, MIP Pharma GmbH, Mylan AB, Navamedic AB, Oresund Pharma ApS, PANPHARMA NORDIC AS, Pfizer Aktiebolag, Sandoz A/S, STADA Nordic ApS, Stragen Nordic A/S, Sun Pharmaceutical Germany GmbH, Tillotts Pharma AB, Unimedic Pharma AB</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2024-07-17Z</t>
-        </is>
-      </c>
-      <c r="C55" s="1" t="n">
-        <v>1063000000</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Amgros I/S</t>
-        </is>
-      </c>
-      <c r="E55" s="1" t="n">
-        <v>1063000000</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Zentiva Denmark ApS</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>DKK</t>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2024-07-17Z</t>
         </is>
       </c>
       <c r="C56" s="1" t="n">
-        <v>244000000</v>
+        <v>1063000000</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Region Skåne, Koncernstab inköp och ekonomistyrning</t>
+          <t>Amgros I/S</t>
         </is>
       </c>
       <c r="E56" s="1" t="n">
-        <v>840000000</v>
+        <v>1063000000</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Øresund Pharma ApS, Vingmed AB, Viatris AB, Unimedic Pharma AB, Recordati AB, Orifarm Generics AB, Orifarm AB, Nordic Drugs Aktiebolag, Navamedic AB, Mölnlycke Health Care AB, Macure Pharma, Krka Sverige AB, Karo Healthcare AB, Janssen-Cilag Aktiebolag, hameln pharma AB, Haleon Sweden AB, Glenmark Pharmaceuticals Nordic AB, GE Healthcare Aktiebolag, G.L. Pharma Nordic Aktiebolag, FrostPharma AB, Exeltis Sverige AB, Ebb Medical, Camurus AB, Bioglan AB, BD Infection Prevention BV, Baxter Medical AB, B.Braun Medical AB, Aspen Pharma Ireland Limited, Aguettant Nordic ApS, Abboxia AB, Bayer Aktiebolag, Øresund Pharma ApS, Vingmed AB, Viatris AB, Unimedic Pharma AB, Recordati AB, Orifarm Generics AB, Orifarm AB, Nordic Drugs Aktiebolag, Navamedic AB, Mölnlycke Health Care AB, Macure Pharma, Krka Sverige AB, Karo Healthcare AB, Janssen-Cilag Aktiebolag, hameln pharma AB, Haleon Sweden AB, Glenmark Pharmaceuticals Nordic AB, GE Healthcare Aktiebolag, G.L. Pharma Nordic Aktiebolag, FrostPharma AB, Exeltis Sverige AB, Ebb Medical, Camurus AB, Bioglan AB, BD Infection Prevention BV, Baxter Medical AB, B.Braun Medical AB, Aspen Pharma Ireland Limited, Aguettant Nordic ApS, Abboxia AB, Bayer Aktiebolag</t>
+          <t>Zentiva Denmark ApS</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>DKK</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>DKK</t>
         </is>
       </c>
     </row>
@@ -2365,6 +2365,44 @@
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="n">
+        <v>211000000</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="E58" s="1" t="n">
+        <v>211000000</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Zentiva Denmark ApS</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2377,7 +2415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3084,6 +3122,44 @@
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>27000000</v>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Region Dalarna</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Exsitec AB</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3095,7 +3171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y67"/>
+  <dimension ref="A1:Y68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4513,12 +4589,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>LOT-0005</t>
+          <t>LOT-0006</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>C: Utvärderingskriterium för delområde 15-17, 20</t>
+          <t>D: Utvärderingskriterium för delområde 18</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -4596,12 +4672,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>LOT-0006</t>
+          <t>LOT-0005</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>D: Utvärderingskriterium för delområde 18</t>
+          <t>C: Utvärderingskriterium för delområde 15-17, 20</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -4679,12 +4755,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>LOT-0003</t>
+          <t>LOT-0004</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>A. Utvärderingskriterium för delområde 1-5, 8-12, 14, 31-46, 48-50</t>
+          <t>B: Utvärderingskriterium för delområde 6-7, 13, 25-30, 47</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -4762,12 +4838,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>LOT-0002</t>
+          <t>LOT-0003</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Kravspecifikation</t>
+          <t>A. Utvärderingskriterium för delområde 1-5, 8-12, 14, 31-46, 48-50</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -4845,12 +4921,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>LOT-0001</t>
+          <t>LOT-0002</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Administrativa föreskrifter - Över tröskelvärde</t>
+          <t>Kravspecifikation</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -4928,12 +5004,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>LOT-0004</t>
+          <t>LOT-0001</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>B: Utvärderingskriterium för delområde 6-7, 13, 25-30, 47</t>
+          <t>Administrativa föreskrifter - Över tröskelvärde</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -6023,12 +6099,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>LOT-0006</t>
+          <t>LOT-0007</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>D. Utvärderingskriterium för delområde 8-10, 13-14, 17-18, 21-24, 27, 29</t>
+          <t>E. Utvärderingskriterium för delområde 30</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -6116,12 +6192,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>LOT-0007</t>
+          <t>LOT-0006</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>E. Utvärderingskriterium för delområde 30</t>
+          <t>D. Utvärderingskriterium för delområde 8-10, 13-14, 17-18, 21-24, 27, 29</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -6751,12 +6827,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>LOT-0001</t>
+          <t>LOT-0004</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Lot No. 1</t>
+          <t>Lot No. 4</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -6764,43 +6840,37 @@
           <t>Won</t>
         </is>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="3" t="n">
+        <v>38000000</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="H40" s="3" t="n">
-        <v>11800000</v>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="J40" s="3" t="n">
+        <v>225775606</v>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="J40" s="3" t="n">
-        <v>11765767</v>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="L40" s="3" t="n">
+        <v>227000000</v>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="L40" s="3" t="n">
-        <v>11800000</v>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
       <c r="N40" s="2" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
@@ -6816,7 +6886,7 @@
         <v>4</v>
       </c>
       <c r="S40" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T40" s="2" t="inlineStr"/>
       <c r="U40" s="2" t="inlineStr">
@@ -6826,12 +6896,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Denmark, Iceland, Norway – Pharmaceutical products – Joint Nordic Procurement of Pharmaceuticals - 2025 - NF2.1303.b</t>
+          <t>Denmark, Iceland, Norway – Pharmaceutical products – Joint Nordic Procurement of Pharmaceuticals - 2025 - NF2.1301.a</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>375509-2025</t>
+          <t>376656-2025</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
@@ -6840,7 +6910,7 @@
         </is>
       </c>
       <c r="Y40" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -6856,12 +6926,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>LOT-0001</t>
+          <t>LOT-0002</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Lot No. 1</t>
+          <t>Lot No. 2</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -6872,7 +6942,7 @@
       <c r="F41" s="3" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="3" t="n">
-        <v>14000000</v>
+        <v>6200000</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
@@ -6955,12 +7025,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>LOT-0002</t>
+          <t>LOT-0003</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Lot No. 2</t>
+          <t>Lot No. 3</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -6968,10 +7038,16 @@
           <t>Won</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
+      <c r="F42" s="3" t="n">
+        <v>12777840</v>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
       <c r="H42" s="3" t="n">
-        <v>6200000</v>
+        <v>136000000</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
@@ -7054,12 +7130,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>LOT-0003</t>
+          <t>LOT-0001</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Lot No. 3</t>
+          <t>Lot No. 1</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -7068,7 +7144,7 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>12777840</v>
+        <v>0</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
@@ -7076,7 +7152,7 @@
         </is>
       </c>
       <c r="H43" s="3" t="n">
-        <v>136000000</v>
+        <v>11800000</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
@@ -7084,7 +7160,7 @@
         </is>
       </c>
       <c r="J43" s="3" t="n">
-        <v>225775606</v>
+        <v>11765767</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
@@ -7092,7 +7168,7 @@
         </is>
       </c>
       <c r="L43" s="3" t="n">
-        <v>227000000</v>
+        <v>11800000</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
@@ -7100,10 +7176,10 @@
         </is>
       </c>
       <c r="N43" s="2" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
@@ -7129,12 +7205,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Denmark, Iceland, Norway – Pharmaceutical products – Joint Nordic Procurement of Pharmaceuticals - 2025 - NF2.1301.a</t>
+          <t>Denmark, Iceland, Norway – Pharmaceutical products – Joint Nordic Procurement of Pharmaceuticals - 2025 - NF2.1303.b</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>376656-2025</t>
+          <t>375509-2025</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
@@ -7159,12 +7235,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>LOT-0004</t>
+          <t>LOT-0001</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Lot No. 4</t>
+          <t>Lot No. 1</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -7175,7 +7251,7 @@
       <c r="F44" s="3" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="3" t="n">
-        <v>38000000</v>
+        <v>14000000</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
@@ -7218,7 +7294,7 @@
         <v>4</v>
       </c>
       <c r="S44" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T44" s="2" t="inlineStr"/>
       <c r="U44" s="2" t="inlineStr">
@@ -7242,7 +7318,7 @@
         </is>
       </c>
       <c r="Y44" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -9324,12 +9400,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>LOT-0002</t>
+          <t>LOT-0001</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Administrativa föreskrifter</t>
+          <t>Kravspec Läkemedel</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -9340,7 +9416,7 @@
       <c r="F65" s="3" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="3" t="n">
-        <v>488000000</v>
+        <v>244000000</v>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
@@ -9376,11 +9452,11 @@
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="R65" s="2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="S65" s="2" t="n">
         <v>42</v>
@@ -9423,12 +9499,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>LOT-0001</t>
+          <t>LOT-0002</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Kravspec Läkemedel</t>
+          <t>Administrativa föreskrifter</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -9439,7 +9515,7 @@
       <c r="F66" s="3" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="3" t="n">
-        <v>244000000</v>
+        <v>488000000</v>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
@@ -9475,11 +9551,11 @@
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2027-02-28</t>
         </is>
       </c>
       <c r="R66" s="2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="S66" s="2" t="n">
         <v>42</v>
@@ -9596,6 +9672,111 @@
         <v>142</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Amgros I/S</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>LOT-0001</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Udbudsnummer 1</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Won</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>211000000</v>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="n">
+        <v>211000000</v>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="n">
+        <v>211000000</v>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>2027-04-01</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>2030-03-31</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="S68" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>Contract Award Notice</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>Denmark – Pharmaceutical products – Amgros 2027 1.1490.a</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>656193-2026</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/ted_procurements.xlsx
+++ b/data/ted_procurements.xlsx
@@ -2985,7 +2985,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
